--- a/results/human_health_breakdown/2025/propanol production, DAC carbon dioxide, wind hydrogen, green ethylene.xlsx
+++ b/results/human_health_breakdown/2025/propanol production, DAC carbon dioxide, wind hydrogen, green ethylene.xlsx
@@ -441,7 +441,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>4.771879279377561E-06</v>
+        <v>4.475450171921547E-06</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>3.633124057962624E-07</v>
+        <v>6.980162978715753E-08</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -526,7 +526,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>2.081613484003897E-09</v>
+        <v>8.89698305954406E-11</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>1.248474678985445E-09</v>
+        <v>3.227826698697177E-10</v>
       </c>
       <c r="E8">
         <v>1</v>
